--- a/diseases/d144/2000-2004.xlsx
+++ b/diseases/d144/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2397,9 +2388,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2941,9 +2929,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -3485,9 +3470,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4029,9 +4011,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4573,9 +4552,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5117,9 +5093,6 @@
       <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -5661,9 +5634,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6205,9 +6175,6 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -6749,9 +6716,6 @@
       <c r="O35" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -7293,9 +7257,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7837,9 +7798,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8233,9 +8191,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8777,9 +8732,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9321,9 +9273,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9865,9 +9814,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10409,9 +10355,6 @@
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -10953,9 +10896,6 @@
       <c r="O58" t="n">
         <v>2</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -11497,9 +11437,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -12041,9 +11978,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12585,9 +12519,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -13129,9 +13060,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13673,9 +13601,6 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -14217,9 +14142,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14761,9 +14683,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15157,9 +15076,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -15701,9 +15617,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -16245,9 +16158,6 @@
       <c r="O87" t="n">
         <v>1</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -16789,9 +16699,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -17333,9 +17240,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -17877,9 +17781,6 @@
       <c r="O96" t="n">
         <v>1</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -18421,9 +18322,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -18965,9 +18863,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -19509,9 +19404,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -20053,9 +19945,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -20597,9 +20486,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -21141,9 +21027,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -21685,9 +21568,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -22081,9 +21961,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -22625,9 +22502,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -23169,9 +23043,6 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -23713,9 +23584,6 @@
       <c r="O128" t="n">
         <v>2</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -24257,9 +24125,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -24801,9 +24666,6 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -25345,9 +25207,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -25889,9 +25748,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -26433,9 +26289,6 @@
       <c r="O143" t="n">
         <v>1</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -26977,9 +26830,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -27521,9 +27371,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -28065,9 +27912,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -28609,9 +28453,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -29005,9 +28846,6 @@
       <c r="O157" t="n">
         <v>2</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -29549,9 +29387,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -30241,9 +30076,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -30785,9 +30617,6 @@
       <c r="O167" t="n">
         <v>1</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -31329,9 +31158,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -31873,9 +31699,6 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -32417,9 +32240,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -32961,9 +32781,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -33505,9 +33322,6 @@
       <c r="O182" t="n">
         <v>1</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -34049,9 +33863,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -34593,9 +34404,6 @@
       <c r="O188" t="n">
         <v>2</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -35136,9 +34944,6 @@
       </c>
       <c r="O191" t="n">
         <v>1</v>
-      </c>
-      <c r="Q191" t="n">
-        <v>0</v>
       </c>
       <c r="R191" t="n">
         <v>0.02177822471534499</v>
